--- a/assets/docs/lop3/Tu nhien va Xa hoi - Lop 3.xlsx
+++ b/assets/docs/lop3/Tu nhien va Xa hoi - Lop 3.xlsx
@@ -1120,7 +1120,7 @@
       <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.3 CB1a: HS sắp xếp đúng thứ tự các ảnh công đoạn và thuật lại quy trình bằng lời của mình.
-QPAN: Giới thiệu truyền thống chống giặc ngoại xâm, gương dũng cảm của thiếu niên, nhi đồng và Bà mẹ Việt Nam anh hùng; kể việc làm của các chú bộ đội, công an giúp dân ở địa phương.</t>
+Học tập và làm theo Bác: Điều 2 “Học tập tốt, lao động tốt” (mạch 2): HS kể một việc của người làm nông nghiệp ở địa phương, nói vì sao phải quý hạt gạo, mớ rau; nhận một việc nhỏ giúp gia đình (nhặt rau, cho gà ăn).</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.1 CB1b: HS xem video tua nhanh và ảnh phóng to, gọi đúng tên các bộ phận của cây, của con vật và nêu được chức năng từng bộ phận.
-STEM: Các bộ phận thực vật (TNXH – Mĩ thuật) — dạy thay cho tiết này.</t>
+STEM: Cây xanh trong chậu trong suốt (TNXH – Toán – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,8 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS xem video tua nhanh và ảnh phóng to, gọi đúng tên các bộ phận của cây, của con vật và nêu được chức năng từng bộ phận.</t>
+          <t>Năng lực số 1.1 CB1b: HS xem video tua nhanh và ảnh phóng to, gọi đúng tên các bộ phận của cây, của con vật và nêu được chức năng từng bộ phận.
+STEM: Cây xanh trong chậu trong suốt (TNXH – Toán – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1492,8 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS xem video tua nhanh và ảnh phóng to, gọi đúng tên các bộ phận của cây, của con vật và nêu được chức năng từng bộ phận.</t>
+          <t>Năng lực số 1.1 CB1b: HS xem video tua nhanh và ảnh phóng to, gọi đúng tên các bộ phận của cây, của con vật và nêu được chức năng từng bộ phận.
+STEM: Cây xanh trong chậu trong suốt (TNXH – Toán – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
